--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/KANSAS_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/KANSAS_2020.xlsx
@@ -1410,7 +1410,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C59">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C115">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C145">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C175">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C180">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C188">
@@ -3829,7 +3829,7 @@
         <v>30</v>
       </c>
       <c r="D193">
-        <v>0.009171507184347295</v>
+        <v>0.009171507184347297</v>
       </c>
     </row>
     <row r="194">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Santiago Tulantepec De Lugo Guerero</t>
+          <t>Santiago Tulantepec De Lugo Guerrero</t>
         </is>
       </c>
       <c r="C273">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C278">
@@ -6061,7 +6061,7 @@
         <v>30</v>
       </c>
       <c r="D317">
-        <v>0.009171507184347295</v>
+        <v>0.009171507184347297</v>
       </c>
     </row>
     <row r="318">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C326">
@@ -7879,7 +7879,7 @@
         <v>30</v>
       </c>
       <c r="D418">
-        <v>0.009171507184347295</v>
+        <v>0.009171507184347297</v>
       </c>
     </row>
     <row r="419">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C428">
